--- a/docs/files/REPORT_FILTRI/Agente Cali Giuseppe - CR LANZANTE DOMENICO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Cali Giuseppe - CR LANZANTE DOMENICO.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -684,13 +684,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1772</v>
+        <v>1736</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1389</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>877</v>
+        <v>862</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1072</v>
+        <v>1054</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>605</v>
@@ -863,14 +863,14 @@
         <v>111</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>35</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>52</v>
@@ -922,7 +922,7 @@
         <v>90</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>2</v>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>46</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>61</v>
@@ -981,7 +981,7 @@
         <v>70</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>2</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>39</v>
@@ -1040,10 +1040,10 @@
         <v>61</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>81</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>37</v>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
